--- a/SCREEN_PRODUCTSTORING.xlsx
+++ b/SCREEN_PRODUCTSTORING.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://winsolgroup-my.sharepoint.com/personal/gwenn_vanthournout_winsol_eu/Documents/_Gwenn/DOCS/AI/_DOCS/PRODUCTSTORING/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://winsolgroup-my.sharepoint.com/personal/gwenn_vanthournout_winsol_eu/Documents/_Gwenn/DOCS/AI/SOCRATES_WEB_DEV/frontend/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="95" documentId="8_{AEEDC2F3-0F41-481B-990B-CA8573AB31BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B268CD37-EA74-4CE6-8C50-DCA38CF6360E}"/>
+  <xr:revisionPtr revIDLastSave="97" documentId="8_{AEEDC2F3-0F41-481B-990B-CA8573AB31BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{176B9B2F-73AE-4B07-9863-C90FEF7E023C}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1E13C84A-EF44-4272-976B-DB216750A179}"/>
   </bookViews>
@@ -949,8 +949,8 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.28515625" customWidth="1"/>
-    <col min="2" max="2" width="35.7109375" customWidth="1"/>
-    <col min="3" max="3" width="35.140625" customWidth="1"/>
+    <col min="2" max="2" width="27.28515625" customWidth="1"/>
+    <col min="3" max="3" width="21.85546875" customWidth="1"/>
     <col min="4" max="4" width="6" customWidth="1"/>
     <col min="5" max="5" width="35.7109375" customWidth="1"/>
     <col min="6" max="6" width="29" customWidth="1"/>

--- a/SCREEN_PRODUCTSTORING.xlsx
+++ b/SCREEN_PRODUCTSTORING.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://winsolgroup-my.sharepoint.com/personal/gwenn_vanthournout_winsol_eu/Documents/_Gwenn/DOCS/AI/SOCRATES_WEB_DEV/frontend/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="97" documentId="8_{AEEDC2F3-0F41-481B-990B-CA8573AB31BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{176B9B2F-73AE-4B07-9863-C90FEF7E023C}"/>
+  <xr:revisionPtr revIDLastSave="101" documentId="8_{AEEDC2F3-0F41-481B-990B-CA8573AB31BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FF5A98D2-4516-4C9B-9671-CC738B913B59}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1E13C84A-EF44-4272-976B-DB216750A179}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{1E13C84A-EF44-4272-976B-DB216750A179}"/>
   </bookViews>
   <sheets>
     <sheet name="SCREEN-PRODUCTSTORING" sheetId="1" r:id="rId1"/>
@@ -476,9 +476,6 @@
     <t xml:space="preserve">Werken de andere sensoren nog? Indien ja, dan is de sensor module nog ok. Indien geen enkele sensor nog werkt, vervang de sensor module. Test: houd de twee zwarte draden kort tegen elkaar (= regensimulatie). In de app zou bij "regen" een 1 moeten verschijnen. </t>
   </si>
   <si>
-    <t>SC05, SC06, SC07, SC22, SC25, SC21</t>
-  </si>
-  <si>
     <t>Check de montage van de assteun (aan de niet-motor kant). De fles van de lager moet naar de oprolas gericht zijn (niet tegen de paal).</t>
   </si>
   <si>
@@ -516,6 +513,9 @@
   </si>
   <si>
     <t>Zet de module in profiel V4.0, voer de screenkalibratie uit, plaats de module opnieuw in V4.1. Indien het probleem aanhoudt, vervang de screenmodule.</t>
+  </si>
+  <si>
+    <t>SC20, SC06, SC05, SC07, SC22, SC25, SC21</t>
   </si>
 </sst>
 </file>
@@ -1051,7 +1051,7 @@
         <v>101</v>
       </c>
       <c r="K3" s="7" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="4" spans="1:12" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -1078,10 +1078,10 @@
         <v>106</v>
       </c>
       <c r="K4" s="7" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="L4" s="7" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="5" spans="1:12" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -1109,7 +1109,7 @@
         <v>103</v>
       </c>
       <c r="K5" s="7" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="6" spans="1:12" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -1165,7 +1165,7 @@
         <v>28</v>
       </c>
       <c r="K7" s="7" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="8" spans="1:12" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -1193,7 +1193,7 @@
         <v>109</v>
       </c>
       <c r="K8" s="7" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="9" spans="1:12" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -1234,7 +1234,7 @@
         <v>38</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>133</v>
+        <v>146</v>
       </c>
       <c r="G10" s="7" t="s">
         <v>36</v>
@@ -1249,7 +1249,7 @@
         <v>112</v>
       </c>
       <c r="K10" s="7" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="11" spans="1:12" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -1333,7 +1333,7 @@
         <v>48</v>
       </c>
       <c r="K13" s="7" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="L13" s="13" t="s">
         <v>130</v>
@@ -1449,7 +1449,7 @@
         <v>67</v>
       </c>
       <c r="K18" s="7" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="19" spans="3:12" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -1515,7 +1515,7 @@
         <v>75</v>
       </c>
       <c r="K21" s="7" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="22" spans="3:12" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -1537,7 +1537,7 @@
         <v>78</v>
       </c>
       <c r="K22" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="23" spans="3:12" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -1581,7 +1581,7 @@
         <v>116</v>
       </c>
       <c r="K24" s="7" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="L24" s="13" t="s">
         <v>130</v>
@@ -1606,7 +1606,7 @@
         <v>120</v>
       </c>
       <c r="K25" s="7" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="26" spans="3:12" s="7" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
